--- a/data/industry/CFM/Index.xlsx
+++ b/data/industry/CFM/Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9208B3-8EE9-46CC-B324-5FD39846C580}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4318973-B867-4645-B497-64D9D4CE05F3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="117">
   <si>
     <t>Flash Wafer</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2088,7 +2088,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB1C738F-C0D7-48DA-9F8D-241372DE5FE0}">
-  <dimension ref="A1:Y34"/>
+  <dimension ref="A1:Y38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="6" bestFit="1" customWidth="1"/>
@@ -2836,6 +2836,86 @@
       </c>
       <c r="F34" s="3">
         <v>2567.14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" s="6">
+        <v>46063</v>
+      </c>
+      <c r="B35" s="6">
+        <v>46063</v>
+      </c>
+      <c r="C35" s="5">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E35" s="3">
+        <v>3406.87</v>
+      </c>
+      <c r="F35" s="3">
+        <v>2605.37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" s="6">
+        <v>46077</v>
+      </c>
+      <c r="B36" s="6">
+        <v>46077</v>
+      </c>
+      <c r="C36" s="5">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E36" s="3">
+        <v>3406.87</v>
+      </c>
+      <c r="F36" s="3">
+        <v>2750.87</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" s="6">
+        <v>46084</v>
+      </c>
+      <c r="B37" s="6">
+        <v>46084</v>
+      </c>
+      <c r="C37" s="5">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E37" s="3">
+        <v>3633.16</v>
+      </c>
+      <c r="F37" s="3">
+        <v>2901.01</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" s="6">
+        <v>46091</v>
+      </c>
+      <c r="B38" s="6">
+        <v>46091</v>
+      </c>
+      <c r="C38" s="5">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E38" s="3">
+        <v>3811.51</v>
+      </c>
+      <c r="F38" s="3">
+        <v>3046.26</v>
       </c>
     </row>
   </sheetData>

--- a/data/industry/CFM/Index.xlsx
+++ b/data/industry/CFM/Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4318973-B867-4645-B497-64D9D4CE05F3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A178A1-1D0F-4CCF-8AC3-F2D6835DAE92}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="117">
   <si>
     <t>Flash Wafer</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -580,10 +580,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Index!$B$2:$B$32</c:f>
+              <c:f>Index!$B$2:$B$1132</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="1131"/>
                 <c:pt idx="0">
                   <c:v>45825</c:v>
                 </c:pt>
@@ -676,16 +676,37 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>46042</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46098</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Index!$E$2:$E$32</c:f>
+              <c:f>Index!$E$2:$E$1132</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="1131"/>
                 <c:pt idx="0">
                   <c:v>678.45</c:v>
                 </c:pt>
@@ -778,6 +799,27 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>3077.44</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>3132.82</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3213.44</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>3406.87</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>3406.87</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>3633.16</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>3811.51</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>3968.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -817,10 +859,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Index!$B$2:$B$32</c:f>
+              <c:f>Index!$B$2:$B$1132</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="1131"/>
                 <c:pt idx="0">
                   <c:v>45825</c:v>
                 </c:pt>
@@ -913,16 +955,37 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>46042</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46098</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Index!$F$2:$F$32</c:f>
+              <c:f>Index!$F$2:$F$1132</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="1131"/>
                 <c:pt idx="0">
                   <c:v>674.2</c:v>
                 </c:pt>
@@ -1015,6 +1078,27 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>2229.8200000000002</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2521.86</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2567.14</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2605.37</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2750.87</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2901.01</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>3046.26</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>3198.66</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2088,7 +2172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB1C738F-C0D7-48DA-9F8D-241372DE5FE0}">
-  <dimension ref="A1:Y38"/>
+  <dimension ref="A1:Y39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="6" bestFit="1" customWidth="1"/>
@@ -2918,9 +3002,30 @@
         <v>3046.26</v>
       </c>
     </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" s="6">
+        <v>46098</v>
+      </c>
+      <c r="B39" s="6">
+        <v>46098</v>
+      </c>
+      <c r="C39" s="5">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E39" s="3">
+        <v>3968.8</v>
+      </c>
+      <c r="F39" s="3">
+        <v>3198.66</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/data/industry/CFM/Index.xlsx
+++ b/data/industry/CFM/Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A178A1-1D0F-4CCF-8AC3-F2D6835DAE92}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63FD51E-652B-4D10-83BD-4ED8A2B54870}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="118">
   <si>
     <t>Flash Wafer</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -400,6 +400,9 @@
   </si>
   <si>
     <t>UTC+8</t>
+  </si>
+  <si>
+    <t>https://www.memorymarket.com/price</t>
   </si>
 </sst>
 </file>
@@ -698,6 +701,9 @@
                 <c:pt idx="37">
                   <c:v>46098</c:v>
                 </c:pt>
+                <c:pt idx="38">
+                  <c:v>46105</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -819,6 +825,9 @@
                   <c:v>3811.51</c:v>
                 </c:pt>
                 <c:pt idx="37">
+                  <c:v>3968.8</c:v>
+                </c:pt>
+                <c:pt idx="38">
                   <c:v>3968.8</c:v>
                 </c:pt>
               </c:numCache>
@@ -977,6 +986,9 @@
                 <c:pt idx="37">
                   <c:v>46098</c:v>
                 </c:pt>
+                <c:pt idx="38">
+                  <c:v>46105</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1099,6 +1111,9 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>3198.66</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>3229.87</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2172,7 +2187,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB1C738F-C0D7-48DA-9F8D-241372DE5FE0}">
-  <dimension ref="A1:Y39"/>
+  <dimension ref="A1:Y40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="6" bestFit="1" customWidth="1"/>
@@ -3022,6 +3037,26 @@
         <v>3198.66</v>
       </c>
     </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" s="6">
+        <v>46105</v>
+      </c>
+      <c r="B40" s="6">
+        <v>46105</v>
+      </c>
+      <c r="C40" s="5">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E40" s="3">
+        <v>3968.8</v>
+      </c>
+      <c r="F40" s="3">
+        <v>3229.87</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3031,7 +3066,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:C94"/>
+  <dimension ref="B1:E94"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -3040,35 +3075,38 @@
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="E2" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
@@ -3076,42 +3114,42 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
@@ -3119,12 +3157,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C16" s="1" t="s">
         <v>18</v>
       </c>

--- a/data/industry/CFM/Index.xlsx
+++ b/data/industry/CFM/Index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63FD51E-652B-4D10-83BD-4ED8A2B54870}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0980D7-FA60-45E5-A7C6-DA9FF50C4963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="118">
   <si>
     <t>Flash Wafer</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -410,29 +410,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -453,7 +453,7 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -477,7 +477,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -485,20 +485,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -510,17 +510,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -538,7 +538,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -704,6 +704,12 @@
                 <c:pt idx="38">
                   <c:v>46105</c:v>
                 </c:pt>
+                <c:pt idx="39">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46119</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -829,6 +835,9 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>3968.8</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>3867.57</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -989,6 +998,12 @@
                 <c:pt idx="38">
                   <c:v>46105</c:v>
                 </c:pt>
+                <c:pt idx="39">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46119</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1114,6 +1129,9 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>3229.87</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>3194.62</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1288,6 +1306,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1295,7 +1314,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2187,20 +2205,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB1C738F-C0D7-48DA-9F8D-241372DE5FE0}">
-  <dimension ref="A1:Y40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y42"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="10.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="10.6328125" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="3"/>
     <col min="26" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="2" customFormat="1">
       <c r="A1" s="13" t="s">
         <v>114</v>
       </c>
@@ -2239,7 +2257,7 @@
       <c r="X1" s="8"/>
       <c r="Y1" s="8"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="6">
         <v>45825</v>
       </c>
@@ -2278,7 +2296,7 @@
       <c r="X2" s="7"/>
       <c r="Y2" s="7"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="6">
         <v>45832</v>
       </c>
@@ -2317,7 +2335,7 @@
       <c r="X3" s="7"/>
       <c r="Y3" s="7"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="6">
         <v>45839</v>
       </c>
@@ -2337,7 +2355,7 @@
         <v>677.73</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="6">
         <v>45846</v>
       </c>
@@ -2357,7 +2375,7 @@
         <v>676.06</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="6">
         <v>45853</v>
       </c>
@@ -2377,7 +2395,7 @@
         <v>676.1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="6">
         <v>45860</v>
       </c>
@@ -2397,7 +2415,7 @@
         <v>674.57</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="6">
         <v>45867</v>
       </c>
@@ -2417,7 +2435,7 @@
         <v>681.42</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="6">
         <v>45874</v>
       </c>
@@ -2437,7 +2455,7 @@
         <v>681.58</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="6">
         <v>45881</v>
       </c>
@@ -2457,7 +2475,7 @@
         <v>681.87</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="6">
         <v>45888</v>
       </c>
@@ -2477,7 +2495,7 @@
         <v>682.04</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="6">
         <v>45895</v>
       </c>
@@ -2497,7 +2515,7 @@
         <v>681.5</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="6">
         <v>45902</v>
       </c>
@@ -2517,7 +2535,7 @@
         <v>679.81</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25">
       <c r="A14" s="6">
         <v>45909</v>
       </c>
@@ -2537,7 +2555,7 @@
         <v>676.9</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25">
       <c r="A15" s="6">
         <v>45916</v>
       </c>
@@ -2557,7 +2575,7 @@
         <v>689.45</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25">
       <c r="A16" s="6">
         <v>45923</v>
       </c>
@@ -2577,7 +2595,7 @@
         <v>711.44</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6">
       <c r="A17" s="6">
         <v>45930</v>
       </c>
@@ -2597,7 +2615,7 @@
         <v>717.66</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="A18" s="6">
         <v>45944</v>
       </c>
@@ -2617,7 +2635,7 @@
         <v>794.72</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6">
       <c r="A19" s="6">
         <v>45951</v>
       </c>
@@ -2637,7 +2655,7 @@
         <v>824.91</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6">
       <c r="A20" s="6">
         <v>45958</v>
       </c>
@@ -2657,7 +2675,7 @@
         <v>930.72</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6">
       <c r="A21" s="6">
         <v>45965</v>
       </c>
@@ -2677,7 +2695,7 @@
         <v>1015.38</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6">
       <c r="A22" s="6">
         <v>45972</v>
       </c>
@@ -2697,7 +2715,7 @@
         <v>1054.43</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6">
       <c r="A23" s="6">
         <v>45979</v>
       </c>
@@ -2717,7 +2735,7 @@
         <v>1217.8800000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6">
       <c r="A24" s="6">
         <v>45986</v>
       </c>
@@ -2737,7 +2755,7 @@
         <v>1438.48</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6">
       <c r="A25" s="6">
         <v>45993</v>
       </c>
@@ -2757,7 +2775,7 @@
         <v>1633.81</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6">
       <c r="A26" s="6">
         <v>46000</v>
       </c>
@@ -2777,7 +2795,7 @@
         <v>1735.53</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6">
       <c r="A27" s="6">
         <v>46007</v>
       </c>
@@ -2797,7 +2815,7 @@
         <v>1742.09</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6">
       <c r="A28" s="6">
         <v>46014</v>
       </c>
@@ -2817,7 +2835,7 @@
         <v>1860.57</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6">
       <c r="A29" s="6">
         <v>46021</v>
       </c>
@@ -2837,7 +2855,7 @@
         <v>1896.1</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6">
       <c r="A30" s="6">
         <v>46028</v>
       </c>
@@ -2857,7 +2875,7 @@
         <v>1982.64</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6">
       <c r="A31" s="6">
         <v>46035</v>
       </c>
@@ -2877,7 +2895,7 @@
         <v>2011.73</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6">
       <c r="A32" s="6">
         <v>46042</v>
       </c>
@@ -2897,7 +2915,7 @@
         <v>2229.8200000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6">
       <c r="A33" s="6">
         <v>46049</v>
       </c>
@@ -2917,7 +2935,7 @@
         <v>2521.86</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6">
       <c r="A34" s="6">
         <v>46056</v>
       </c>
@@ -2937,7 +2955,7 @@
         <v>2567.14</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6">
       <c r="A35" s="6">
         <v>46063</v>
       </c>
@@ -2957,7 +2975,7 @@
         <v>2605.37</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6">
       <c r="A36" s="6">
         <v>46077</v>
       </c>
@@ -2977,7 +2995,7 @@
         <v>2750.87</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6">
       <c r="A37" s="6">
         <v>46084</v>
       </c>
@@ -2997,7 +3015,7 @@
         <v>2901.01</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6">
       <c r="A38" s="6">
         <v>46091</v>
       </c>
@@ -3017,7 +3035,7 @@
         <v>3046.26</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6">
       <c r="A39" s="6">
         <v>46098</v>
       </c>
@@ -3037,7 +3055,7 @@
         <v>3198.66</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6">
       <c r="A40" s="6">
         <v>46105</v>
       </c>
@@ -3055,6 +3073,40 @@
       </c>
       <c r="F40" s="3">
         <v>3229.87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="6">
+        <v>46112</v>
+      </c>
+      <c r="B41" s="6">
+        <v>46112</v>
+      </c>
+      <c r="C41" s="5">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3867.57</v>
+      </c>
+      <c r="F41" s="3">
+        <v>3194.62</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="6">
+        <v>46119</v>
+      </c>
+      <c r="B42" s="6">
+        <v>46119</v>
+      </c>
+      <c r="C42" s="5">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -3067,20 +3119,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:E94"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="12.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.90625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:5">
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:5">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -3091,22 +3143,22 @@
         <v>117</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:5">
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:5">
       <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:5">
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:5">
       <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
@@ -3114,42 +3166,42 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:5">
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:5">
       <c r="C8" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:5">
       <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:5">
       <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:5">
       <c r="C11" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:5">
       <c r="C12" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:5">
       <c r="C13" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:5">
       <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
@@ -3157,32 +3209,32 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:5">
       <c r="C15" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:5">
       <c r="C16" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:3">
       <c r="C17" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:3">
       <c r="C18" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:3">
       <c r="C19" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:3">
       <c r="B20" s="2" t="s">
         <v>22</v>
       </c>
@@ -3190,37 +3242,37 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:3">
       <c r="C21" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:3">
       <c r="C22" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:3">
       <c r="C23" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:3">
       <c r="C24" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:3">
       <c r="C25" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:3">
       <c r="C26" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:3">
       <c r="B27" s="2" t="s">
         <v>30</v>
       </c>
@@ -3228,17 +3280,17 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:3">
       <c r="C28" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:3">
       <c r="C29" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:3">
       <c r="B30" s="2" t="s">
         <v>34</v>
       </c>
@@ -3246,47 +3298,47 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:3">
       <c r="C31" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:3">
       <c r="C32" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:3">
       <c r="C33" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:3">
       <c r="C34" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:3">
       <c r="C35" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:3">
       <c r="C36" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:3">
       <c r="C37" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:3">
       <c r="C38" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:3">
       <c r="B39" s="2" t="s">
         <v>44</v>
       </c>
@@ -3294,47 +3346,47 @@
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:3">
       <c r="C40" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:3">
       <c r="C41" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:3">
       <c r="C42" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:3">
       <c r="C43" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:3">
       <c r="C44" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:3">
       <c r="C45" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:3">
       <c r="C46" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:3">
       <c r="C47" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:3">
       <c r="B48" s="2" t="s">
         <v>54</v>
       </c>
@@ -3342,27 +3394,27 @@
         <v>55</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:3">
       <c r="C49" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:3">
       <c r="C50" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:3">
       <c r="C51" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:3">
       <c r="C52" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:3">
       <c r="B53" s="2" t="s">
         <v>60</v>
       </c>
@@ -3370,32 +3422,32 @@
         <v>61</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:3">
       <c r="C54" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:3">
       <c r="C55" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:3">
       <c r="C56" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:3">
       <c r="C57" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:3">
       <c r="C58" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:3">
       <c r="B59" s="2" t="s">
         <v>67</v>
       </c>
@@ -3403,17 +3455,17 @@
         <v>68</v>
       </c>
     </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:3">
       <c r="C60" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:3">
       <c r="C61" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:3">
       <c r="B62" s="2" t="s">
         <v>71</v>
       </c>
@@ -3421,22 +3473,22 @@
         <v>72</v>
       </c>
     </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:3">
       <c r="C63" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:3">
       <c r="C64" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:3">
       <c r="C65" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:3">
       <c r="B66" s="2" t="s">
         <v>76</v>
       </c>
@@ -3444,22 +3496,22 @@
         <v>77</v>
       </c>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:3">
       <c r="C67" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:3">
       <c r="C68" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:3">
       <c r="C69" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:3">
       <c r="B70" s="2" t="s">
         <v>81</v>
       </c>
@@ -3467,47 +3519,47 @@
         <v>82</v>
       </c>
     </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:3">
       <c r="C71" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:3">
       <c r="C72" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:3">
       <c r="C73" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:3">
       <c r="C74" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:3">
       <c r="C75" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:3">
       <c r="C76" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:3">
       <c r="C77" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:3">
       <c r="C78" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:3">
       <c r="B79" s="2" t="s">
         <v>91</v>
       </c>
@@ -3515,32 +3567,32 @@
         <v>92</v>
       </c>
     </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:3">
       <c r="C80" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:3">
       <c r="C81" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:3">
       <c r="C82" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:3">
       <c r="C83" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:3">
       <c r="C84" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:3">
       <c r="B85" s="2" t="s">
         <v>98</v>
       </c>
@@ -3548,47 +3600,47 @@
         <v>99</v>
       </c>
     </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:3">
       <c r="C86" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:3">
       <c r="C87" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="88" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:3">
       <c r="C88" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:3">
       <c r="C89" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="90" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:3">
       <c r="C90" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:3">
       <c r="C91" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="92" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:3">
       <c r="C92" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="93" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:3">
       <c r="C93" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="94" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:3">
       <c r="C94" s="1" t="s">
         <v>108</v>
       </c>
@@ -3602,7 +3654,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF528F66-5C7C-40F6-B437-A79684695F91}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="16384" width="9" style="14"/>
   </cols>

--- a/data/industry/CFM/Index.xlsx
+++ b/data/industry/CFM/Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6A0BB0E-5B94-454D-A395-073D20BA77B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A9030F9-0FEE-46EB-96A5-9CAB86535678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="118">
   <si>
     <t>Flash Wafer</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -716,6 +716,9 @@
                 <c:pt idx="42">
                   <c:v>46133</c:v>
                 </c:pt>
+                <c:pt idx="43">
+                  <c:v>46140</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -853,6 +856,9 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>3977.5</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>3938.46</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1025,6 +1031,9 @@
                 <c:pt idx="42">
                   <c:v>46133</c:v>
                 </c:pt>
+                <c:pt idx="43">
+                  <c:v>46140</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1162,6 +1171,9 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>3142.68</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>3059.92</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2238,7 +2250,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB1C738F-C0D7-48DA-9F8D-241372DE5FE0}">
-  <dimension ref="A1:Y44"/>
+  <dimension ref="A1:Y45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="6" bestFit="1" customWidth="1"/>
@@ -3186,6 +3198,26 @@
       </c>
       <c r="F44" s="3">
         <v>3142.68</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45" s="6">
+        <v>46140</v>
+      </c>
+      <c r="B45" s="6">
+        <v>46140</v>
+      </c>
+      <c r="C45" s="5">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E45" s="3">
+        <v>3938.46</v>
+      </c>
+      <c r="F45" s="3">
+        <v>3059.92</v>
       </c>
     </row>
   </sheetData>

--- a/data/industry/CFM/Index.xlsx
+++ b/data/industry/CFM/Index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A9030F9-0FEE-46EB-96A5-9CAB86535678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBF1461C-EB31-4A6B-875E-EAE841569C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32415" yWindow="1860" windowWidth="21600" windowHeight="10875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="118">
   <si>
     <t>Flash Wafer</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -410,29 +410,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -453,7 +453,7 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -477,7 +477,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -485,20 +485,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -510,10 +510,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -583,10 +583,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Index!$B$2:$B$1132</c:f>
+              <c:f>Index!$B$2:$B$1131</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1131"/>
+                <c:ptCount val="1130"/>
                 <c:pt idx="0">
                   <c:v>45825</c:v>
                 </c:pt>
@@ -718,16 +718,28 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46154</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46161</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Index!$E$2:$E$1132</c:f>
+              <c:f>Index!$E$2:$E$1131</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="1131"/>
+                <c:ptCount val="1130"/>
                 <c:pt idx="0">
                   <c:v>678.45</c:v>
                 </c:pt>
@@ -859,6 +871,18 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>3938.46</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>3945.39</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>3932.44</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>3913.14</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>3913.14</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -898,10 +922,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Index!$B$2:$B$1132</c:f>
+              <c:f>Index!$B$2:$B$1131</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1131"/>
+                <c:ptCount val="1130"/>
                 <c:pt idx="0">
                   <c:v>45825</c:v>
                 </c:pt>
@@ -1033,16 +1057,28 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46154</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46161</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Index!$F$2:$F$1132</c:f>
+              <c:f>Index!$F$2:$F$1131</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="1131"/>
+                <c:ptCount val="1130"/>
                 <c:pt idx="0">
                   <c:v>674.2</c:v>
                 </c:pt>
@@ -1174,6 +1210,18 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>3059.92</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>3029.7</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>3019.44</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>3014.54</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>3014.38</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2250,20 +2298,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB1C738F-C0D7-48DA-9F8D-241372DE5FE0}">
-  <dimension ref="A1:Y45"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y49"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.19921875" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.8984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="10.59765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="10.5546875" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="3"/>
     <col min="26" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="2" customFormat="1">
       <c r="A1" s="13" t="s">
         <v>114</v>
       </c>
@@ -2302,7 +2350,7 @@
       <c r="X1" s="8"/>
       <c r="Y1" s="8"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="6">
         <v>45825</v>
       </c>
@@ -2341,7 +2389,7 @@
       <c r="X2" s="7"/>
       <c r="Y2" s="7"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="6">
         <v>45832</v>
       </c>
@@ -2380,7 +2428,7 @@
       <c r="X3" s="7"/>
       <c r="Y3" s="7"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="6">
         <v>45839</v>
       </c>
@@ -2400,7 +2448,7 @@
         <v>677.73</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="6">
         <v>45846</v>
       </c>
@@ -2420,7 +2468,7 @@
         <v>676.06</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="6">
         <v>45853</v>
       </c>
@@ -2440,7 +2488,7 @@
         <v>676.1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="6">
         <v>45860</v>
       </c>
@@ -2460,7 +2508,7 @@
         <v>674.57</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="6">
         <v>45867</v>
       </c>
@@ -2480,7 +2528,7 @@
         <v>681.42</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="6">
         <v>45874</v>
       </c>
@@ -2500,7 +2548,7 @@
         <v>681.58</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="6">
         <v>45881</v>
       </c>
@@ -2520,7 +2568,7 @@
         <v>681.87</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="6">
         <v>45888</v>
       </c>
@@ -2540,7 +2588,7 @@
         <v>682.04</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="6">
         <v>45895</v>
       </c>
@@ -2560,7 +2608,7 @@
         <v>681.5</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="6">
         <v>45902</v>
       </c>
@@ -2580,7 +2628,7 @@
         <v>679.81</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25">
       <c r="A14" s="6">
         <v>45909</v>
       </c>
@@ -2600,7 +2648,7 @@
         <v>676.9</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25">
       <c r="A15" s="6">
         <v>45916</v>
       </c>
@@ -2620,7 +2668,7 @@
         <v>689.45</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25">
       <c r="A16" s="6">
         <v>45923</v>
       </c>
@@ -2640,7 +2688,7 @@
         <v>711.44</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6">
       <c r="A17" s="6">
         <v>45930</v>
       </c>
@@ -2660,7 +2708,7 @@
         <v>717.66</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="A18" s="6">
         <v>45944</v>
       </c>
@@ -2680,7 +2728,7 @@
         <v>794.72</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6">
       <c r="A19" s="6">
         <v>45951</v>
       </c>
@@ -2700,7 +2748,7 @@
         <v>824.91</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6">
       <c r="A20" s="6">
         <v>45958</v>
       </c>
@@ -2720,7 +2768,7 @@
         <v>930.72</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6">
       <c r="A21" s="6">
         <v>45965</v>
       </c>
@@ -2740,7 +2788,7 @@
         <v>1015.38</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6">
       <c r="A22" s="6">
         <v>45972</v>
       </c>
@@ -2760,7 +2808,7 @@
         <v>1054.43</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6">
       <c r="A23" s="6">
         <v>45979</v>
       </c>
@@ -2780,7 +2828,7 @@
         <v>1217.8800000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6">
       <c r="A24" s="6">
         <v>45986</v>
       </c>
@@ -2800,7 +2848,7 @@
         <v>1438.48</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6">
       <c r="A25" s="6">
         <v>45993</v>
       </c>
@@ -2820,7 +2868,7 @@
         <v>1633.81</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6">
       <c r="A26" s="6">
         <v>46000</v>
       </c>
@@ -2840,7 +2888,7 @@
         <v>1735.53</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6">
       <c r="A27" s="6">
         <v>46007</v>
       </c>
@@ -2860,7 +2908,7 @@
         <v>1742.09</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6">
       <c r="A28" s="6">
         <v>46014</v>
       </c>
@@ -2880,7 +2928,7 @@
         <v>1860.57</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6">
       <c r="A29" s="6">
         <v>46021</v>
       </c>
@@ -2900,7 +2948,7 @@
         <v>1896.1</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6">
       <c r="A30" s="6">
         <v>46028</v>
       </c>
@@ -2920,7 +2968,7 @@
         <v>1982.64</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6">
       <c r="A31" s="6">
         <v>46035</v>
       </c>
@@ -2940,7 +2988,7 @@
         <v>2011.73</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6">
       <c r="A32" s="6">
         <v>46042</v>
       </c>
@@ -2960,7 +3008,7 @@
         <v>2229.8200000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6">
       <c r="A33" s="6">
         <v>46049</v>
       </c>
@@ -2980,7 +3028,7 @@
         <v>2521.86</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6">
       <c r="A34" s="6">
         <v>46056</v>
       </c>
@@ -3000,7 +3048,7 @@
         <v>2567.14</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6">
       <c r="A35" s="6">
         <v>46063</v>
       </c>
@@ -3020,7 +3068,7 @@
         <v>2605.37</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6">
       <c r="A36" s="6">
         <v>46077</v>
       </c>
@@ -3040,7 +3088,7 @@
         <v>2750.87</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6">
       <c r="A37" s="6">
         <v>46084</v>
       </c>
@@ -3060,7 +3108,7 @@
         <v>2901.01</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6">
       <c r="A38" s="6">
         <v>46091</v>
       </c>
@@ -3080,7 +3128,7 @@
         <v>3046.26</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6">
       <c r="A39" s="6">
         <v>46098</v>
       </c>
@@ -3100,7 +3148,7 @@
         <v>3198.66</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6">
       <c r="A40" s="6">
         <v>46105</v>
       </c>
@@ -3120,7 +3168,7 @@
         <v>3229.87</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6">
       <c r="A41" s="6">
         <v>46112</v>
       </c>
@@ -3140,7 +3188,7 @@
         <v>3194.62</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6">
       <c r="A42" s="6">
         <v>46119</v>
       </c>
@@ -3160,7 +3208,7 @@
         <v>3194.62</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6">
       <c r="A43" s="6">
         <v>46126</v>
       </c>
@@ -3180,7 +3228,7 @@
         <v>3164.63</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6">
       <c r="A44" s="6">
         <v>46133</v>
       </c>
@@ -3200,7 +3248,7 @@
         <v>3142.68</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6">
       <c r="A45" s="6">
         <v>46140</v>
       </c>
@@ -3218,6 +3266,86 @@
       </c>
       <c r="F45" s="3">
         <v>3059.92</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="6">
+        <v>46154</v>
+      </c>
+      <c r="B46" s="6">
+        <v>46154</v>
+      </c>
+      <c r="C46" s="5">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3945.39</v>
+      </c>
+      <c r="F46" s="3">
+        <v>3029.7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="6">
+        <v>46161</v>
+      </c>
+      <c r="B47" s="6">
+        <v>46161</v>
+      </c>
+      <c r="C47" s="5">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E47" s="3">
+        <v>3932.44</v>
+      </c>
+      <c r="F47" s="3">
+        <v>3019.44</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="6">
+        <v>46168</v>
+      </c>
+      <c r="B48" s="6">
+        <v>46168</v>
+      </c>
+      <c r="C48" s="5">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3913.14</v>
+      </c>
+      <c r="F48" s="3">
+        <v>3014.54</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="6">
+        <v>46175</v>
+      </c>
+      <c r="B49" s="6">
+        <v>46175</v>
+      </c>
+      <c r="C49" s="5">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E49" s="3">
+        <v>3913.14</v>
+      </c>
+      <c r="F49" s="3">
+        <v>3014.38</v>
       </c>
     </row>
   </sheetData>
@@ -3230,20 +3358,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:E94"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="12.8984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:5">
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:5">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -3254,22 +3382,22 @@
         <v>117</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:5">
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:5">
       <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:5">
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:5">
       <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
@@ -3277,42 +3405,42 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:5">
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:5">
       <c r="C8" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:5">
       <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:5">
       <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:5">
       <c r="C11" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:5">
       <c r="C12" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:5">
       <c r="C13" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:5">
       <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
@@ -3320,32 +3448,32 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:5">
       <c r="C15" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:5">
       <c r="C16" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:3">
       <c r="C17" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:3">
       <c r="C18" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:3">
       <c r="C19" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:3">
       <c r="B20" s="2" t="s">
         <v>22</v>
       </c>
@@ -3353,37 +3481,37 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:3">
       <c r="C21" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:3">
       <c r="C22" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:3">
       <c r="C23" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:3">
       <c r="C24" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:3">
       <c r="C25" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:3">
       <c r="C26" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:3">
       <c r="B27" s="2" t="s">
         <v>30</v>
       </c>
@@ -3391,17 +3519,17 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:3">
       <c r="C28" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:3">
       <c r="C29" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:3">
       <c r="B30" s="2" t="s">
         <v>34</v>
       </c>
@@ -3409,47 +3537,47 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:3">
       <c r="C31" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:3">
       <c r="C32" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:3">
       <c r="C33" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:3">
       <c r="C34" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:3">
       <c r="C35" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:3">
       <c r="C36" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:3">
       <c r="C37" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:3">
       <c r="C38" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:3">
       <c r="B39" s="2" t="s">
         <v>44</v>
       </c>
@@ -3457,47 +3585,47 @@
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:3">
       <c r="C40" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:3">
       <c r="C41" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:3">
       <c r="C42" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:3">
       <c r="C43" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:3">
       <c r="C44" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:3">
       <c r="C45" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:3">
       <c r="C46" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:3">
       <c r="C47" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:3">
       <c r="B48" s="2" t="s">
         <v>54</v>
       </c>
@@ -3505,27 +3633,27 @@
         <v>55</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:3">
       <c r="C49" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:3">
       <c r="C50" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:3">
       <c r="C51" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:3">
       <c r="C52" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:3">
       <c r="B53" s="2" t="s">
         <v>60</v>
       </c>
@@ -3533,32 +3661,32 @@
         <v>61</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:3">
       <c r="C54" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:3">
       <c r="C55" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:3">
       <c r="C56" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:3">
       <c r="C57" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:3">
       <c r="C58" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:3">
       <c r="B59" s="2" t="s">
         <v>67</v>
       </c>
@@ -3566,17 +3694,17 @@
         <v>68</v>
       </c>
     </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:3">
       <c r="C60" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:3">
       <c r="C61" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:3">
       <c r="B62" s="2" t="s">
         <v>71</v>
       </c>
@@ -3584,22 +3712,22 @@
         <v>72</v>
       </c>
     </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:3">
       <c r="C63" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:3">
       <c r="C64" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:3">
       <c r="C65" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:3">
       <c r="B66" s="2" t="s">
         <v>76</v>
       </c>
@@ -3607,22 +3735,22 @@
         <v>77</v>
       </c>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:3">
       <c r="C67" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:3">
       <c r="C68" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:3">
       <c r="C69" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:3">
       <c r="B70" s="2" t="s">
         <v>81</v>
       </c>
@@ -3630,47 +3758,47 @@
         <v>82</v>
       </c>
     </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:3">
       <c r="C71" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:3">
       <c r="C72" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:3">
       <c r="C73" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:3">
       <c r="C74" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:3">
       <c r="C75" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:3">
       <c r="C76" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:3">
       <c r="C77" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:3">
       <c r="C78" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:3">
       <c r="B79" s="2" t="s">
         <v>91</v>
       </c>
@@ -3678,32 +3806,32 @@
         <v>92</v>
       </c>
     </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:3">
       <c r="C80" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:3">
       <c r="C81" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:3">
       <c r="C82" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:3">
       <c r="C83" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:3">
       <c r="C84" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:3">
       <c r="B85" s="2" t="s">
         <v>98</v>
       </c>
@@ -3711,47 +3839,47 @@
         <v>99</v>
       </c>
     </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:3">
       <c r="C86" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:3">
       <c r="C87" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="88" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:3">
       <c r="C88" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:3">
       <c r="C89" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="90" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:3">
       <c r="C90" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:3">
       <c r="C91" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="92" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:3">
       <c r="C92" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="93" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:3">
       <c r="C93" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="94" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:3">
       <c r="C94" s="1" t="s">
         <v>108</v>
       </c>
@@ -3765,7 +3893,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF528F66-5C7C-40F6-B437-A79684695F91}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="16384" width="9" style="14"/>
   </cols>
